--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.8182,0.0590,0.0214,0.0783</t>
-  </si>
-  <si>
-    <t>0.0119,0.0064,0.0018,0.9934</t>
-  </si>
-  <si>
-    <t>0.8343,0.0189,0.0444,0.0738</t>
-  </si>
-  <si>
-    <t>0.1634,0.0168,0.0035,0.9288</t>
-  </si>
-  <si>
-    <t>0.9892,0.0054,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9858,0.0065,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9891,0.0053,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9863,0.0045,0.0005,0.0040</t>
-  </si>
-  <si>
-    <t>0.9905,0.0080,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9869,0.0062,0.0003,0.0025</t>
-  </si>
-  <si>
-    <t>0.9860,0.0077,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.9897,0.0039,0.0005,0.0022</t>
-  </si>
-  <si>
-    <t>0.4864,0.0480,0.5247,0.0350</t>
-  </si>
-  <si>
-    <t>0.4101,0.0924,0.5682,0.0128</t>
-  </si>
-  <si>
-    <t>0.4580,0.1330,0.5085,0.0092</t>
-  </si>
-  <si>
-    <t>0.0773,0.1611,0.8271,0.0067</t>
-  </si>
-  <si>
-    <t>0.6604,0.0980,0.2605,0.0172</t>
-  </si>
-  <si>
-    <t>0.0108,0.9852,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.0681,0.9157,0.0305,0.0005</t>
-  </si>
-  <si>
-    <t>0.6123,0.4851,0.0167,0.0040</t>
-  </si>
-  <si>
-    <t>0.0978,0.9244,0.0104,0.0004</t>
-  </si>
-  <si>
-    <t>0.0107,0.9854,0.0105,0.0001</t>
-  </si>
-  <si>
-    <t>0.4366,0.0539,0.5320,0.0552</t>
-  </si>
-  <si>
-    <t>0.4490,0.0310,0.3501,0.1751</t>
-  </si>
-  <si>
-    <t>0.0102,0.0076,0.9762,0.0155</t>
-  </si>
-  <si>
-    <t>0.5357,0.0527,0.4350,0.0460</t>
-  </si>
-  <si>
-    <t>0.0748,0.0109,0.9125,0.0287</t>
-  </si>
-  <si>
-    <t>0.4086,0.0167,0.6540,0.0321</t>
-  </si>
-  <si>
-    <t>0.0769,0.0098,0.8891,0.0439</t>
-  </si>
-  <si>
-    <t>0.6439,0.4075,0.0259,0.0042</t>
-  </si>
-  <si>
-    <t>0.6316,0.2220,0.1867,0.0056</t>
-  </si>
-  <si>
-    <t>0.0398,0.0603,0.9328,0.0180</t>
-  </si>
-  <si>
-    <t>0.0699,0.6232,0.5041,0.0010</t>
-  </si>
-  <si>
-    <t>0.8232,0.1073,0.0508,0.0172</t>
-  </si>
-  <si>
-    <t>0.6604,0.1325,0.1872,0.0038</t>
-  </si>
-  <si>
-    <t>0.7629,0.2694,0.0228,0.0013</t>
-  </si>
-  <si>
-    <t>0.0378,0.9193,0.1428,0.0041</t>
-  </si>
-  <si>
-    <t>0.0820,0.3450,0.6810,0.0464</t>
-  </si>
-  <si>
-    <t>0.0075,0.0037,0.7725,0.3553</t>
-  </si>
-  <si>
-    <t>0.0919,0.1289,0.7941,0.0548</t>
-  </si>
-  <si>
-    <t>0.0314,0.0052,0.5746,0.5244</t>
-  </si>
-  <si>
-    <t>0.0493,0.0745,0.9024,0.0233</t>
-  </si>
-  <si>
-    <t>0.0275,0.7759,0.5530,0.0083</t>
-  </si>
-  <si>
-    <t>0.0767,0.1240,0.8281,0.0168</t>
-  </si>
-  <si>
-    <t>0.2509,0.2133,0.0474,0.6877</t>
-  </si>
-  <si>
-    <t>0.0232,0.9321,0.1271,0.0059</t>
-  </si>
-  <si>
-    <t>0.0076,0.9662,0.1309,0.0005</t>
-  </si>
-  <si>
-    <t>0.0104,0.9571,0.1402,0.0013</t>
-  </si>
-  <si>
-    <t>0.0309,0.0616,0.9169,0.0446</t>
-  </si>
-  <si>
-    <t>0.0185,0.2224,0.9365,0.0025</t>
-  </si>
-  <si>
-    <t>0.0629,0.0298,0.8494,0.1059</t>
-  </si>
-  <si>
-    <t>0.1578,0.0112,0.8816,0.0076</t>
-  </si>
-  <si>
-    <t>0.0078,0.0141,0.9559,0.0569</t>
-  </si>
-  <si>
-    <t>0.1170,0.0196,0.8768,0.0161</t>
-  </si>
-  <si>
-    <t>0.9218,0.1220,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.9818,0.0071,0.0040,0.0028</t>
-  </si>
-  <si>
-    <t>0.9691,0.0239,0.0057,0.0025</t>
-  </si>
-  <si>
-    <t>0.0748,0.0644,0.9210,0.0046</t>
-  </si>
-  <si>
-    <t>0.9853,0.0084,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.9911,0.0041,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9603,0.0399,0.0049,0.0020</t>
-  </si>
-  <si>
-    <t>0.0062,0.4350,0.9439,0.0012</t>
-  </si>
-  <si>
-    <t>0.0468,0.0988,0.8900,0.0184</t>
-  </si>
-  <si>
-    <t>0.0049,0.0113,0.8966,0.1669</t>
-  </si>
-  <si>
-    <t>0.0082,0.6536,0.8982,0.0032</t>
-  </si>
-  <si>
-    <t>0.0135,0.0301,0.9700,0.0111</t>
-  </si>
-  <si>
-    <t>0.0482,0.8937,0.0845,0.0021</t>
-  </si>
-  <si>
-    <t>0.0087,0.9868,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.8822,0.0366,0.0705,0.0181</t>
-  </si>
-  <si>
-    <t>0.4749,0.1053,0.4727,0.0060</t>
-  </si>
-  <si>
-    <t>0.2640,0.6158,0.0846,0.0029</t>
-  </si>
-  <si>
-    <t>0.0085,0.7290,0.8072,0.0016</t>
-  </si>
-  <si>
-    <t>0.0302,0.5091,0.7318,0.0019</t>
-  </si>
-  <si>
-    <t>0.0216,0.7692,0.6532,0.0064</t>
-  </si>
-  <si>
-    <t>0.0221,0.4814,0.8376,0.0034</t>
-  </si>
-  <si>
-    <t>0.1112,0.0132,0.0309,0.9160</t>
-  </si>
-  <si>
-    <t>0.0051,0.0079,0.0005,0.9975</t>
-  </si>
-  <si>
-    <t>0.0127,0.0029,0.0021,0.9933</t>
-  </si>
-  <si>
-    <t>0.0529,0.0256,0.0122,0.9678</t>
-  </si>
-  <si>
-    <t>0.0669,0.0095,0.0033,0.9729</t>
-  </si>
-  <si>
-    <t>0.0244,0.0057,0.0111,0.9795</t>
-  </si>
-  <si>
-    <t>0.0117,0.7118,0.7980,0.0023</t>
-  </si>
-  <si>
-    <t>0.0116,0.4099,0.9413,0.0026</t>
-  </si>
-  <si>
-    <t>0.0624,0.2108,0.8214,0.0071</t>
-  </si>
-  <si>
-    <t>0.0357,0.2066,0.8932,0.0160</t>
-  </si>
-  <si>
-    <t>0.0096,0.6871,0.8735,0.0022</t>
-  </si>
-  <si>
-    <t>0.0187,0.6312,0.7823,0.0054</t>
-  </si>
-  <si>
-    <t>0.9906,0.0033,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.9528,0.0594,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.9903,0.0051,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9855,0.0097,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9893,0.0051,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.9909,0.0053,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9862,0.0112,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9777,0.0280,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9931,0.0014,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.9934,0.0022,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9921,0.0031,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9903,0.0033,0.0004,0.0021</t>
-  </si>
-  <si>
-    <t>0.9925,0.0030,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9898,0.0063,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9912,0.0036,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9910,0.0028,0.0002,0.0029</t>
-  </si>
-  <si>
-    <t>0.0081,0.0053,0.9671,0.0446</t>
-  </si>
-  <si>
-    <t>0.0249,0.0096,0.9629,0.0158</t>
-  </si>
-  <si>
-    <t>0.4600,0.0738,0.4062,0.1441</t>
-  </si>
-  <si>
-    <t>0.0864,0.0219,0.8954,0.0106</t>
-  </si>
-  <si>
-    <t>0.0980,0.9304,0.0069,0.0007</t>
-  </si>
-  <si>
-    <t>0.2182,0.8690,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.1648,0.9001,0.0057,0.0009</t>
-  </si>
-  <si>
-    <t>0.3087,0.7921,0.0068,0.0021</t>
-  </si>
-  <si>
-    <t>0.1653,0.8659,0.0149,0.0011</t>
-  </si>
-  <si>
-    <t>0.0243,0.9773,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.8430,0.2158,0.0075,0.0003</t>
-  </si>
-  <si>
-    <t>0.4817,0.3135,0.2645,0.0366</t>
-  </si>
-  <si>
-    <t>0.2654,0.0403,0.7461,0.0097</t>
-  </si>
-  <si>
-    <t>0.3210,0.4698,0.2792,0.0309</t>
-  </si>
-  <si>
-    <t>0.7222,0.1348,0.1155,0.0338</t>
-  </si>
-  <si>
-    <t>0.5084,0.0774,0.1008,0.3553</t>
-  </si>
-  <si>
-    <t>0.0020,0.9901,0.0455,0.0003</t>
-  </si>
-  <si>
-    <t>0.0227,0.9017,0.2793,0.0055</t>
-  </si>
-  <si>
-    <t>0.0770,0.8497,0.1164,0.0827</t>
-  </si>
-  <si>
-    <t>0.0012,0.9594,0.7358,0.0002</t>
-  </si>
-  <si>
-    <t>0.0384,0.9345,0.0566,0.0005</t>
-  </si>
-  <si>
-    <t>0.7310,0.3281,0.0203,0.0012</t>
-  </si>
-  <si>
-    <t>0.7258,0.3008,0.0261,0.0014</t>
-  </si>
-  <si>
-    <t>0.9646,0.0249,0.0062,0.0039</t>
-  </si>
-  <si>
-    <t>0.9781,0.0195,0.0027,0.0013</t>
-  </si>
-  <si>
-    <t>0.9850,0.0033,0.0008,0.0077</t>
-  </si>
-  <si>
-    <t>0.9742,0.0131,0.0017,0.0054</t>
-  </si>
-  <si>
-    <t>0.9856,0.0068,0.0016,0.0025</t>
-  </si>
-  <si>
-    <t>0.9279,0.0787,0.0113,0.0013</t>
-  </si>
-  <si>
-    <t>0.9765,0.0114,0.0058,0.0029</t>
-  </si>
-  <si>
-    <t>0.9801,0.0112,0.0016,0.0032</t>
-  </si>
-  <si>
-    <t>0.0147,0.1485,0.9526,0.0069</t>
-  </si>
-  <si>
-    <t>0.0303,0.5391,0.7634,0.0051</t>
-  </si>
-  <si>
-    <t>0.0786,0.0532,0.8930,0.0197</t>
-  </si>
-  <si>
-    <t>0.1265,0.1228,0.7551,0.0095</t>
-  </si>
-  <si>
-    <t>0.6108,0.3013,0.1106,0.0255</t>
-  </si>
-  <si>
-    <t>0.6750,0.1315,0.2023,0.0357</t>
-  </si>
-  <si>
-    <t>0.6069,0.0076,0.5132,0.0188</t>
-  </si>
-  <si>
-    <t>0.4369,0.3150,0.3015,0.0244</t>
-  </si>
-  <si>
-    <t>0.0500,0.0136,0.0157,0.9640</t>
-  </si>
-  <si>
-    <t>0.0012,0.0009,0.0012,0.9985</t>
-  </si>
-  <si>
-    <t>0.0156,0.0044,0.0068,0.9874</t>
-  </si>
-  <si>
-    <t>0.0515,0.0101,0.0105,0.9679</t>
-  </si>
-  <si>
-    <t>0.0254,0.7254,0.6753,0.0070</t>
-  </si>
-  <si>
-    <t>0.9571,0.0620,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.6434,0.5091,0.0065,0.0051</t>
-  </si>
-  <si>
-    <t>0.9451,0.0132,0.0023,0.0299</t>
-  </si>
-  <si>
-    <t>0.9009,0.1374,0.0051,0.0031</t>
-  </si>
-  <si>
-    <t>0.9795,0.0099,0.0033,0.0031</t>
-  </si>
-  <si>
-    <t>0.8061,0.0140,0.0211,0.1479</t>
-  </si>
-  <si>
-    <t>0.9779,0.0261,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.1958,0.2452,0.6358,0.0806</t>
-  </si>
-  <si>
-    <t>0.6383,0.0030,0.0049,0.5093</t>
-  </si>
-  <si>
-    <t>0.9552,0.0029,0.0046,0.0220</t>
-  </si>
-  <si>
-    <t>0.6451,0.1756,0.1945,0.0107</t>
-  </si>
-  <si>
-    <t>0.8917,0.0809,0.0295,0.0069</t>
-  </si>
-  <si>
-    <t>0.8049,0.2107,0.0171,0.0057</t>
-  </si>
-  <si>
-    <t>0.3058,0.6335,0.1116,0.0186</t>
-  </si>
-  <si>
-    <t>0.2336,0.6999,0.0961,0.0032</t>
-  </si>
-  <si>
-    <t>0.8140,0.1331,0.0656,0.0097</t>
-  </si>
-  <si>
-    <t>0.9870,0.0057,0.0007,0.0026</t>
-  </si>
-  <si>
-    <t>0.9872,0.0089,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9755,0.0156,0.0011,0.0028</t>
-  </si>
-  <si>
-    <t>0.9810,0.0042,0.0014,0.0078</t>
-  </si>
-  <si>
-    <t>0.9670,0.0261,0.0034,0.0022</t>
-  </si>
-  <si>
-    <t>0.9839,0.0086,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.9789,0.0038,0.0004,0.0122</t>
-  </si>
-  <si>
-    <t>0.9815,0.0041,0.0007,0.0094</t>
-  </si>
-  <si>
-    <t>0.2868,0.7743,0.0154,0.0020</t>
-  </si>
-  <si>
-    <t>0.5539,0.5962,0.0091,0.0011</t>
-  </si>
-  <si>
-    <t>0.3496,0.7500,0.0110,0.0014</t>
-  </si>
-  <si>
-    <t>0.7463,0.0886,0.2439,0.0084</t>
-  </si>
-  <si>
-    <t>0.8571,0.2296,0.0060,0.0008</t>
-  </si>
-  <si>
-    <t>0.9345,0.0717,0.0058,0.0021</t>
-  </si>
-  <si>
-    <t>0.9448,0.0729,0.0055,0.0011</t>
-  </si>
-  <si>
-    <t>0.8696,0.1294,0.0177,0.0032</t>
-  </si>
-  <si>
-    <t>0.0070,0.1469,0.9758,0.0014</t>
-  </si>
-  <si>
-    <t>0.7697,0.3163,0.0126,0.0016</t>
-  </si>
-  <si>
-    <t>0.0237,0.0106,0.9779,0.0031</t>
-  </si>
-  <si>
-    <t>0.0521,0.1080,0.9055,0.0128</t>
-  </si>
-  <si>
-    <t>0.2073,0.0166,0.8566,0.0153</t>
-  </si>
-  <si>
-    <t>0.0199,0.2019,0.9063,0.0138</t>
-  </si>
-  <si>
-    <t>0.1655,0.1149,0.7773,0.0115</t>
-  </si>
-  <si>
-    <t>0.0408,0.0057,0.9714,0.0037</t>
-  </si>
-  <si>
-    <t>0.0348,0.0380,0.9428,0.0106</t>
-  </si>
-  <si>
-    <t>0.5735,0.0907,0.3949,0.0368</t>
-  </si>
-  <si>
-    <t>0.4115,0.2441,0.4071,0.0136</t>
-  </si>
-  <si>
-    <t>0.2618,0.2685,0.5285,0.0112</t>
-  </si>
-  <si>
-    <t>0.2658,0.4339,0.2736,0.0050</t>
-  </si>
-  <si>
-    <t>0.1925,0.3309,0.5206,0.0072</t>
-  </si>
-  <si>
-    <t>0.7568,0.0480,0.2288,0.0201</t>
-  </si>
-  <si>
-    <t>0.3937,0.4793,0.2212,0.0292</t>
-  </si>
-  <si>
-    <t>0.5583,0.1066,0.4069,0.0302</t>
-  </si>
-  <si>
-    <t>0.6404,0.4941,0.0064,0.0024</t>
-  </si>
-  <si>
-    <t>0.9670,0.0465,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.8760,0.1745,0.0100,0.0011</t>
-  </si>
-  <si>
-    <t>0.9829,0.0089,0.0005,0.0038</t>
-  </si>
-  <si>
-    <t>0.9065,0.1254,0.0083,0.0015</t>
-  </si>
-  <si>
-    <t>0.4641,0.2519,0.3154,0.0168</t>
-  </si>
-  <si>
-    <t>0.7488,0.0316,0.2994,0.0105</t>
-  </si>
-  <si>
-    <t>0.7114,0.0257,0.3229,0.0213</t>
-  </si>
-  <si>
-    <t>0.6526,0.0231,0.3911,0.0203</t>
-  </si>
-  <si>
-    <t>0.4568,0.2715,0.3251,0.0614</t>
-  </si>
-  <si>
-    <t>0.1783,0.1463,0.7264,0.0281</t>
-  </si>
-  <si>
-    <t>0.0734,0.1067,0.8565,0.0398</t>
-  </si>
-  <si>
-    <t>0.0398,0.0363,0.9402,0.0215</t>
-  </si>
-  <si>
-    <t>0.0451,0.0228,0.7157,0.2922</t>
-  </si>
-  <si>
-    <t>0.0787,0.1041,0.8266,0.0642</t>
-  </si>
-  <si>
-    <t>0.9843,0.0083,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.9878,0.0074,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9877,0.0066,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.9902,0.0047,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.9861,0.0024,0.0002,0.0066</t>
-  </si>
-  <si>
-    <t>0.9892,0.0075,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9879,0.0070,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9861,0.0084,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.4558,0.0300,0.6475,0.0102</t>
-  </si>
-  <si>
-    <t>0.3076,0.3192,0.3788,0.0034</t>
-  </si>
-  <si>
-    <t>0.8845,0.1076,0.0169,0.0099</t>
-  </si>
-  <si>
-    <t>0.0337,0.0100,0.9701,0.0055</t>
-  </si>
-  <si>
-    <t>0.0026,0.0040,0.9813,0.0325</t>
-  </si>
-  <si>
-    <t>0.2481,0.0581,0.7279,0.0075</t>
-  </si>
-  <si>
-    <t>0.0059,0.0097,0.9840,0.0148</t>
-  </si>
-  <si>
-    <t>0.1145,0.3141,0.6242,0.0227</t>
-  </si>
-  <si>
-    <t>0.0062,0.0088,0.9886,0.0065</t>
-  </si>
-  <si>
-    <t>0.0339,0.0874,0.8881,0.0329</t>
-  </si>
-  <si>
-    <t>0.5043,0.2192,0.3256,0.0472</t>
-  </si>
-  <si>
-    <t>0.6750,0.0435,0.2646,0.0674</t>
-  </si>
-  <si>
-    <t>0.4912,0.0169,0.5709,0.0360</t>
-  </si>
-  <si>
-    <t>0.7670,0.0550,0.1803,0.0098</t>
-  </si>
-  <si>
-    <t>0.9735,0.0231,0.0038,0.0016</t>
-  </si>
-  <si>
-    <t>0.9862,0.0140,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9915,0.0038,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9701,0.0345,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9398,0.0878,0.0026,0.0010</t>
-  </si>
-  <si>
-    <t>0.9801,0.0174,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.9832,0.0187,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9867,0.0079,0.0006,0.0019</t>
-  </si>
-  <si>
-    <t>0.0378,0.5163,0.7208,0.0045</t>
-  </si>
-  <si>
-    <t>0.0181,0.0742,0.9526,0.0093</t>
-  </si>
-  <si>
-    <t>0.0253,0.1409,0.9105,0.0116</t>
-  </si>
-  <si>
-    <t>0.2047,0.0764,0.7016,0.0407</t>
-  </si>
-  <si>
-    <t>0.0721,0.0126,0.9212,0.0166</t>
-  </si>
-  <si>
-    <t>0.1137,0.0096,0.1637,0.7695</t>
-  </si>
-  <si>
-    <t>0.1942,0.0547,0.6862,0.1238</t>
-  </si>
-  <si>
-    <t>0.0154,0.0129,0.7275,0.3517</t>
-  </si>
-  <si>
-    <t>0.7591,0.0054,0.0126,0.2570</t>
-  </si>
-  <si>
-    <t>0.0401,0.1626,0.0157,0.9635</t>
-  </si>
-  <si>
-    <t>0.0247,0.0025,0.0029,0.9886</t>
-  </si>
-  <si>
-    <t>0.0124,0.0029,0.0016,0.9941</t>
-  </si>
-  <si>
-    <t>0.0058,0.0041,0.0009,0.9968</t>
-  </si>
-  <si>
-    <t>0.7680,0.0218,0.0301,0.1451</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.7314,0.0139,0.0222,0.2341</t>
+  </si>
+  <si>
+    <t>0.0266,0.0026,0.0047,0.9841</t>
+  </si>
+  <si>
+    <t>0.7967,0.0304,0.0138,0.1062</t>
+  </si>
+  <si>
+    <t>0.1722,0.0072,0.0046,0.9260</t>
+  </si>
+  <si>
+    <t>0.9934,0.0022,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9930,0.0034,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9780,0.0184,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.9840,0.0057,0.0021,0.0032</t>
+  </si>
+  <si>
+    <t>0.9922,0.0047,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9887,0.0087,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9911,0.0053,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9943,0.0027,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.5418,0.2403,0.2538,0.0789</t>
+  </si>
+  <si>
+    <t>0.2650,0.3382,0.4871,0.0087</t>
+  </si>
+  <si>
+    <t>0.1680,0.2846,0.6415,0.0014</t>
+  </si>
+  <si>
+    <t>0.0491,0.0547,0.9433,0.0025</t>
+  </si>
+  <si>
+    <t>0.6637,0.1467,0.2191,0.0193</t>
+  </si>
+  <si>
+    <t>0.0137,0.9818,0.0094,0.0003</t>
+  </si>
+  <si>
+    <t>0.0197,0.9762,0.0105,0.0001</t>
+  </si>
+  <si>
+    <t>0.2674,0.8243,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.1144,0.9166,0.0086,0.0006</t>
+  </si>
+  <si>
+    <t>0.0449,0.9598,0.0082,0.0002</t>
+  </si>
+  <si>
+    <t>0.4173,0.0314,0.4845,0.1022</t>
+  </si>
+  <si>
+    <t>0.6919,0.0279,0.1804,0.0622</t>
+  </si>
+  <si>
+    <t>0.0161,0.0096,0.9712,0.0158</t>
+  </si>
+  <si>
+    <t>0.3845,0.0800,0.5889,0.0073</t>
+  </si>
+  <si>
+    <t>0.1939,0.0082,0.8434,0.0225</t>
+  </si>
+  <si>
+    <t>0.1328,0.0094,0.8464,0.0439</t>
+  </si>
+  <si>
+    <t>0.0341,0.0161,0.8901,0.1128</t>
+  </si>
+  <si>
+    <t>0.4581,0.6083,0.0220,0.0030</t>
+  </si>
+  <si>
+    <t>0.5387,0.3055,0.2053,0.0310</t>
+  </si>
+  <si>
+    <t>0.0038,0.0217,0.9749,0.0276</t>
+  </si>
+  <si>
+    <t>0.0363,0.9447,0.0257,0.0004</t>
+  </si>
+  <si>
+    <t>0.9081,0.0516,0.0292,0.0091</t>
+  </si>
+  <si>
+    <t>0.5184,0.0313,0.5605,0.0066</t>
+  </si>
+  <si>
+    <t>0.7421,0.3253,0.0157,0.0015</t>
+  </si>
+  <si>
+    <t>0.0319,0.9139,0.2065,0.0029</t>
+  </si>
+  <si>
+    <t>0.0323,0.4823,0.5840,0.0959</t>
+  </si>
+  <si>
+    <t>0.0158,0.0222,0.8335,0.1792</t>
+  </si>
+  <si>
+    <t>0.0592,0.1097,0.8409,0.0752</t>
+  </si>
+  <si>
+    <t>0.0235,0.0087,0.8563,0.1825</t>
+  </si>
+  <si>
+    <t>0.0593,0.0929,0.8854,0.0085</t>
+  </si>
+  <si>
+    <t>0.0211,0.8500,0.4204,0.0042</t>
+  </si>
+  <si>
+    <t>0.0336,0.0144,0.9486,0.0169</t>
+  </si>
+  <si>
+    <t>0.1141,0.2691,0.0079,0.8529</t>
+  </si>
+  <si>
+    <t>0.0196,0.9463,0.0782,0.0019</t>
+  </si>
+  <si>
+    <t>0.0060,0.9686,0.1465,0.0007</t>
+  </si>
+  <si>
+    <t>0.0096,0.9703,0.0437,0.0027</t>
+  </si>
+  <si>
+    <t>0.0534,0.0765,0.9064,0.0125</t>
+  </si>
+  <si>
+    <t>0.0074,0.0323,0.9687,0.0265</t>
+  </si>
+  <si>
+    <t>0.0661,0.0214,0.8914,0.0497</t>
+  </si>
+  <si>
+    <t>0.2797,0.0103,0.7986,0.0101</t>
+  </si>
+  <si>
+    <t>0.0748,0.0427,0.8930,0.0388</t>
+  </si>
+  <si>
+    <t>0.1024,0.2655,0.6830,0.0367</t>
+  </si>
+  <si>
+    <t>0.9565,0.0471,0.0032,0.0022</t>
+  </si>
+  <si>
+    <t>0.9849,0.0043,0.0014,0.0049</t>
+  </si>
+  <si>
+    <t>0.9855,0.0070,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.0451,0.0739,0.9406,0.0104</t>
+  </si>
+  <si>
+    <t>0.9831,0.0123,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9786,0.0184,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.9867,0.0046,0.0009,0.0031</t>
+  </si>
+  <si>
+    <t>0.0152,0.2487,0.9359,0.0026</t>
+  </si>
+  <si>
+    <t>0.0483,0.0480,0.9218,0.0149</t>
+  </si>
+  <si>
+    <t>0.0493,0.1330,0.8833,0.0190</t>
+  </si>
+  <si>
+    <t>0.0087,0.5969,0.9091,0.0027</t>
+  </si>
+  <si>
+    <t>0.0170,0.0078,0.9623,0.0266</t>
+  </si>
+  <si>
+    <t>0.0690,0.8450,0.1483,0.0050</t>
+  </si>
+  <si>
+    <t>0.0140,0.9765,0.0090,0.0002</t>
+  </si>
+  <si>
+    <t>0.8043,0.0374,0.0828,0.0938</t>
+  </si>
+  <si>
+    <t>0.6440,0.3518,0.0561,0.0076</t>
+  </si>
+  <si>
+    <t>0.1034,0.3538,0.6547,0.0043</t>
+  </si>
+  <si>
+    <t>0.0075,0.6385,0.9069,0.0012</t>
+  </si>
+  <si>
+    <t>0.0301,0.7036,0.6425,0.0059</t>
+  </si>
+  <si>
+    <t>0.0231,0.8046,0.6214,0.0101</t>
+  </si>
+  <si>
+    <t>0.0095,0.7680,0.8120,0.0029</t>
+  </si>
+  <si>
+    <t>0.0341,0.0033,0.0063,0.9796</t>
+  </si>
+  <si>
+    <t>0.0064,0.0070,0.0013,0.9960</t>
+  </si>
+  <si>
+    <t>0.0046,0.0114,0.0019,0.9957</t>
+  </si>
+  <si>
+    <t>0.0159,0.0100,0.0019,0.9917</t>
+  </si>
+  <si>
+    <t>0.0224,0.0077,0.0018,0.9903</t>
+  </si>
+  <si>
+    <t>0.0412,0.0195,0.0037,0.9795</t>
+  </si>
+  <si>
+    <t>0.0127,0.6448,0.8518,0.0031</t>
+  </si>
+  <si>
+    <t>0.0110,0.1518,0.9642,0.0057</t>
+  </si>
+  <si>
+    <t>0.0390,0.4005,0.8177,0.0119</t>
+  </si>
+  <si>
+    <t>0.0444,0.1227,0.8348,0.0715</t>
+  </si>
+  <si>
+    <t>0.0085,0.5209,0.9096,0.0014</t>
+  </si>
+  <si>
+    <t>0.0242,0.5527,0.8095,0.0093</t>
+  </si>
+  <si>
+    <t>0.9872,0.0072,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9878,0.0103,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9889,0.0087,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9900,0.0042,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9884,0.0036,0.0008,0.0025</t>
+  </si>
+  <si>
+    <t>0.9935,0.0037,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9840,0.0129,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9898,0.0080,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9906,0.0034,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9921,0.0021,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9926,0.0012,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.9960,0.0014,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9906,0.0058,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9947,0.0026,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9922,0.0015,0.0001,0.0032</t>
+  </si>
+  <si>
+    <t>0.9913,0.0029,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.0099,0.0097,0.9804,0.0125</t>
+  </si>
+  <si>
+    <t>0.1620,0.0406,0.8235,0.0198</t>
+  </si>
+  <si>
+    <t>0.4333,0.0973,0.2318,0.2972</t>
+  </si>
+  <si>
+    <t>0.4663,0.0109,0.5895,0.0309</t>
+  </si>
+  <si>
+    <t>0.1508,0.9078,0.0048,0.0005</t>
+  </si>
+  <si>
+    <t>0.1682,0.8950,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.1303,0.9030,0.0088,0.0011</t>
+  </si>
+  <si>
+    <t>0.0819,0.9091,0.0243,0.0007</t>
+  </si>
+  <si>
+    <t>0.0381,0.9680,0.0053,0.0002</t>
+  </si>
+  <si>
+    <t>0.0437,0.9663,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.6099,0.4658,0.0152,0.0012</t>
+  </si>
+  <si>
+    <t>0.5168,0.2975,0.2475,0.0494</t>
+  </si>
+  <si>
+    <t>0.4063,0.0153,0.6857,0.0173</t>
+  </si>
+  <si>
+    <t>0.2723,0.5700,0.0556,0.2450</t>
+  </si>
+  <si>
+    <t>0.3697,0.1329,0.5781,0.0055</t>
+  </si>
+  <si>
+    <t>0.5695,0.2669,0.1303,0.1185</t>
+  </si>
+  <si>
+    <t>0.0079,0.9702,0.1397,0.0006</t>
+  </si>
+  <si>
+    <t>0.0098,0.9647,0.0736,0.0036</t>
+  </si>
+  <si>
+    <t>0.3553,0.4941,0.2246,0.0510</t>
+  </si>
+  <si>
+    <t>0.0031,0.9765,0.2209,0.0005</t>
+  </si>
+  <si>
+    <t>0.0135,0.9559,0.1212,0.0004</t>
+  </si>
+  <si>
+    <t>0.7621,0.3177,0.0131,0.0012</t>
+  </si>
+  <si>
+    <t>0.6703,0.4335,0.0157,0.0016</t>
+  </si>
+  <si>
+    <t>0.9595,0.0284,0.0030,0.0043</t>
+  </si>
+  <si>
+    <t>0.9827,0.0094,0.0014,0.0033</t>
+  </si>
+  <si>
+    <t>0.9850,0.0055,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.9746,0.0071,0.0018,0.0066</t>
+  </si>
+  <si>
+    <t>0.9915,0.0042,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9529,0.0157,0.0263,0.0050</t>
+  </si>
+  <si>
+    <t>0.9831,0.0108,0.0031,0.0011</t>
+  </si>
+  <si>
+    <t>0.9849,0.0070,0.0015,0.0025</t>
+  </si>
+  <si>
+    <t>0.0161,0.3263,0.9051,0.0063</t>
+  </si>
+  <si>
+    <t>0.0447,0.0989,0.9141,0.0060</t>
+  </si>
+  <si>
+    <t>0.0450,0.2600,0.8481,0.0022</t>
+  </si>
+  <si>
+    <t>0.0365,0.2583,0.8663,0.0039</t>
+  </si>
+  <si>
+    <t>0.6600,0.0868,0.0766,0.2287</t>
+  </si>
+  <si>
+    <t>0.5012,0.0271,0.5451,0.0497</t>
+  </si>
+  <si>
+    <t>0.3838,0.1296,0.5534,0.0099</t>
+  </si>
+  <si>
+    <t>0.5275,0.2843,0.2117,0.0250</t>
+  </si>
+  <si>
+    <t>0.1104,0.0100,0.0096,0.9464</t>
+  </si>
+  <si>
+    <t>0.0007,0.0033,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0047,0.0636,0.0024,0.9937</t>
+  </si>
+  <si>
+    <t>0.0841,0.0088,0.0055,0.9618</t>
+  </si>
+  <si>
+    <t>0.0243,0.5740,0.7692,0.0212</t>
+  </si>
+  <si>
+    <t>0.9526,0.0312,0.0039,0.0081</t>
+  </si>
+  <si>
+    <t>0.4399,0.6632,0.0148,0.0021</t>
+  </si>
+  <si>
+    <t>0.9770,0.0056,0.0012,0.0109</t>
+  </si>
+  <si>
+    <t>0.5578,0.5903,0.0079,0.0011</t>
+  </si>
+  <si>
+    <t>0.9719,0.0154,0.0043,0.0032</t>
+  </si>
+  <si>
+    <t>0.7374,0.0105,0.0260,0.2217</t>
+  </si>
+  <si>
+    <t>0.9655,0.0165,0.0028,0.0081</t>
+  </si>
+  <si>
+    <t>0.0851,0.4538,0.6584,0.0620</t>
+  </si>
+  <si>
+    <t>0.8572,0.0027,0.0028,0.1526</t>
+  </si>
+  <si>
+    <t>0.9316,0.0175,0.0314,0.0105</t>
+  </si>
+  <si>
+    <t>0.5212,0.4338,0.0664,0.0066</t>
+  </si>
+  <si>
+    <t>0.8521,0.1410,0.0222,0.0055</t>
+  </si>
+  <si>
+    <t>0.3828,0.6658,0.0280,0.0028</t>
+  </si>
+  <si>
+    <t>0.6267,0.3104,0.0782,0.0093</t>
+  </si>
+  <si>
+    <t>0.7103,0.2491,0.0769,0.0169</t>
+  </si>
+  <si>
+    <t>0.7203,0.2711,0.0376,0.0057</t>
+  </si>
+  <si>
+    <t>0.9834,0.0142,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.9851,0.0114,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9922,0.0037,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9841,0.0043,0.0004,0.0075</t>
+  </si>
+  <si>
+    <t>0.9782,0.0153,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.9805,0.0142,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9821,0.0132,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9864,0.0032,0.0004,0.0054</t>
+  </si>
+  <si>
+    <t>0.1114,0.8941,0.0198,0.0011</t>
+  </si>
+  <si>
+    <t>0.8252,0.2768,0.0071,0.0009</t>
+  </si>
+  <si>
+    <t>0.4748,0.6034,0.0152,0.0018</t>
+  </si>
+  <si>
+    <t>0.8140,0.0988,0.1187,0.0063</t>
+  </si>
+  <si>
+    <t>0.9705,0.0357,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.7957,0.2078,0.0364,0.0073</t>
+  </si>
+  <si>
+    <t>0.9609,0.0676,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.7731,0.3527,0.0069,0.0017</t>
+  </si>
+  <si>
+    <t>0.0108,0.0476,0.9773,0.0052</t>
+  </si>
+  <si>
+    <t>0.9777,0.0199,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.0123,0.0042,0.9889,0.0018</t>
+  </si>
+  <si>
+    <t>0.0420,0.0429,0.9291,0.0252</t>
+  </si>
+  <si>
+    <t>0.2000,0.1473,0.6925,0.0334</t>
+  </si>
+  <si>
+    <t>0.0307,0.1516,0.9117,0.0194</t>
+  </si>
+  <si>
+    <t>0.0342,0.0096,0.9623,0.0081</t>
+  </si>
+  <si>
+    <t>0.0742,0.0045,0.9548,0.0034</t>
+  </si>
+  <si>
+    <t>0.1466,0.0445,0.8482,0.0072</t>
+  </si>
+  <si>
+    <t>0.6177,0.0776,0.3618,0.0243</t>
+  </si>
+  <si>
+    <t>0.4152,0.0390,0.6775,0.0086</t>
+  </si>
+  <si>
+    <t>0.5522,0.0696,0.4468,0.0267</t>
+  </si>
+  <si>
+    <t>0.1579,0.2485,0.6845,0.0016</t>
+  </si>
+  <si>
+    <t>0.2126,0.3677,0.4482,0.0107</t>
+  </si>
+  <si>
+    <t>0.5076,0.2226,0.2580,0.0054</t>
+  </si>
+  <si>
+    <t>0.5352,0.0424,0.4930,0.0156</t>
+  </si>
+  <si>
+    <t>0.7834,0.0499,0.1918,0.0092</t>
+  </si>
+  <si>
+    <t>0.8373,0.2710,0.0051,0.0011</t>
+  </si>
+  <si>
+    <t>0.8182,0.3256,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.9483,0.0611,0.0058,0.0015</t>
+  </si>
+  <si>
+    <t>0.9682,0.0389,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9362,0.0973,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.5193,0.2137,0.3256,0.0806</t>
+  </si>
+  <si>
+    <t>0.6709,0.0828,0.3120,0.0158</t>
+  </si>
+  <si>
+    <t>0.6950,0.1118,0.2109,0.0279</t>
+  </si>
+  <si>
+    <t>0.6139,0.0143,0.2656,0.0945</t>
+  </si>
+  <si>
+    <t>0.8291,0.0286,0.1098,0.0293</t>
+  </si>
+  <si>
+    <t>0.0257,0.0458,0.9265,0.0483</t>
+  </si>
+  <si>
+    <t>0.0966,0.0540,0.7966,0.1035</t>
+  </si>
+  <si>
+    <t>0.0343,0.0427,0.8974,0.0828</t>
+  </si>
+  <si>
+    <t>0.0741,0.0650,0.7355,0.1891</t>
+  </si>
+  <si>
+    <t>0.0618,0.0919,0.8160,0.0836</t>
+  </si>
+  <si>
+    <t>0.9905,0.0070,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9768,0.0205,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9901,0.0040,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9892,0.0064,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9644,0.0415,0.0044,0.0010</t>
+  </si>
+  <si>
+    <t>0.9916,0.0063,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9883,0.0032,0.0005,0.0042</t>
+  </si>
+  <si>
+    <t>0.9791,0.0107,0.0028,0.0024</t>
+  </si>
+  <si>
+    <t>0.4799,0.0181,0.7111,0.0050</t>
+  </si>
+  <si>
+    <t>0.2274,0.6656,0.1769,0.0068</t>
+  </si>
+  <si>
+    <t>0.9432,0.0217,0.0260,0.0050</t>
+  </si>
+  <si>
+    <t>0.0832,0.0565,0.8757,0.0162</t>
+  </si>
+  <si>
+    <t>0.0025,0.0051,0.9786,0.0350</t>
+  </si>
+  <si>
+    <t>0.1398,0.1966,0.6504,0.0214</t>
+  </si>
+  <si>
+    <t>0.0009,0.0031,0.9905,0.0163</t>
+  </si>
+  <si>
+    <t>0.3105,0.2298,0.4799,0.0317</t>
+  </si>
+  <si>
+    <t>0.0034,0.0079,0.9933,0.0032</t>
+  </si>
+  <si>
+    <t>0.0442,0.0361,0.9350,0.0085</t>
+  </si>
+  <si>
+    <t>0.2374,0.0812,0.7390,0.0192</t>
+  </si>
+  <si>
+    <t>0.6706,0.0422,0.3684,0.0144</t>
+  </si>
+  <si>
+    <t>0.5924,0.0227,0.4209,0.0357</t>
+  </si>
+  <si>
+    <t>0.7967,0.0137,0.2180,0.0166</t>
+  </si>
+  <si>
+    <t>0.9879,0.0096,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9734,0.0291,0.0020,0.0012</t>
+  </si>
+  <si>
+    <t>0.9798,0.0139,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.9783,0.0276,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9869,0.0051,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9897,0.0095,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9829,0.0149,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9891,0.0043,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.1574,0.0982,0.7654,0.0027</t>
+  </si>
+  <si>
+    <t>0.0188,0.0337,0.9313,0.0505</t>
+  </si>
+  <si>
+    <t>0.0454,0.0514,0.9224,0.0073</t>
+  </si>
+  <si>
+    <t>0.1180,0.4979,0.5431,0.0168</t>
+  </si>
+  <si>
+    <t>0.0090,0.0046,0.9499,0.0646</t>
+  </si>
+  <si>
+    <t>0.1651,0.0142,0.1369,0.7359</t>
+  </si>
+  <si>
+    <t>0.4297,0.1130,0.4763,0.0843</t>
+  </si>
+  <si>
+    <t>0.0245,0.0155,0.8683,0.1299</t>
+  </si>
+  <si>
+    <t>0.5345,0.0123,0.0865,0.4573</t>
+  </si>
+  <si>
+    <t>0.0185,0.0169,0.0069,0.9843</t>
+  </si>
+  <si>
+    <t>0.1262,0.0041,0.0036,0.9497</t>
+  </si>
+  <si>
+    <t>0.0104,0.0037,0.0018,0.9940</t>
+  </si>
+  <si>
+    <t>0.0047,0.0012,0.0005,0.9979</t>
+  </si>
+  <si>
+    <t>0.6529,0.1468,0.1328,0.1390</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2287,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2312,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2522,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,10 +2550,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2581,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,10 +3656,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,10 +5126,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5336,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,10 +5420,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
